--- a/StructureDefinition-Urval-fynd-resistens-laboratoriemedicin.xlsx
+++ b/StructureDefinition-Urval-fynd-resistens-laboratoriemedicin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Urval-fynd-resistens-laboratoriemedicin.xlsx
+++ b/StructureDefinition-Urval-fynd-resistens-laboratoriemedicin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Urval fynd resistens laboratoriemedicin ).</t>
+    <t>Urval ur Snomed CT (1.2.752.116.2.1.1) för att beskriva resultat av undersökning av resistens mot antibiotika inom laboratoriemedicin.
+OID: 1.2.752.129.5.1.10
+Refset-ID: 500041000057108</t>
   </si>
   <si>
     <t>Purpose</t>
